--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-03).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-03).xlsx
@@ -912,17 +912,17 @@
   </si>
   <si>
     <t>214
-181</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>R$ 870.654,28</t>
-  </si>
-  <si>
-    <t>R$ 4.558,40
-R$ 4.647,03</t>
+182</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>R$ 874.451,26</t>
+  </si>
+  <si>
+    <t>R$ 4.554,43
+R$ 4.642,36</t>
   </si>
   <si>
     <t>(3.9%)
@@ -935,10 +935,10 @@
     <t>(9.6%)</t>
   </si>
   <si>
-    <t>(14.8%)</t>
-  </si>
-  <si>
-    <t>(55.4%)</t>
+    <t>(14.2%)</t>
+  </si>
+  <si>
+    <t>(54.7%)</t>
   </si>
   <si>
     <t>3.9%</t>
@@ -950,7 +950,7 @@
     <t>26.8</t>
   </si>
   <si>
-    <t>74.2%</t>
+    <t>74.0%</t>
   </si>
   <si>
     <t>9.9%</t>
@@ -962,19 +962,19 @@
     <t>6.8</t>
   </si>
   <si>
-    <t>12.4</t>
+    <t>12.3</t>
   </si>
   <si>
     <t>18.8</t>
   </si>
   <si>
-    <t>73.0%</t>
-  </si>
-  <si>
-    <t>-R$ 28.288,85</t>
-  </si>
-  <si>
-    <t>2.97</t>
+    <t>72.9%</t>
+  </si>
+  <si>
+    <t>-R$ 28.390,15</t>
+  </si>
+  <si>
+    <t>2.95</t>
   </si>
   <si>
     <t>3.52</t>
@@ -8758,7 +8758,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>44</v>
@@ -8794,27 +8794,61 @@
       <c t="s" r="N58" s="4">
         <v>52</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-      <c r="X58" s="8"/>
-      <c r="Y58" s="6"/>
-      <c r="Z58" s="6"/>
-      <c r="AA58" s="8"/>
-      <c r="AB58" s="8"/>
+      <c r="O58" s="5">
+        <v>3796.98</v>
+      </c>
+      <c r="P58" s="5">
+        <v>3796.98</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>-0.03846660318875228</v>
+      </c>
+      <c r="R58" s="7">
+        <v>43</v>
+      </c>
+      <c r="S58" s="6">
+        <v>-0.15686274509803921</v>
+      </c>
+      <c r="T58" s="6">
+        <v>1.2757555741668378</v>
+      </c>
+      <c r="U58" s="6">
+        <v>0.91898782716790717</v>
+      </c>
+      <c r="V58" s="6">
+        <v>0.019398574656700852</v>
+      </c>
+      <c r="W58" s="6">
+        <v>-0.0018920299817223162</v>
+      </c>
+      <c r="X58" s="8">
+        <v>31.288333333333334</v>
+      </c>
+      <c r="Y58" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="Z58" s="6">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="AA58" s="8">
+        <v>4.5898365853658536</v>
+      </c>
+      <c r="AB58" s="8">
+        <v>8.4355566666666668</v>
+      </c>
       <c r="AC58" s="8">
         <v>13.757220999999999</v>
       </c>
-      <c r="AD58" s="8"/>
-      <c r="AE58" s="6"/>
+      <c r="AD58" s="8">
+        <v>20.693333333333332</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>0.46666666666666667</v>
+      </c>
       <c r="AF58" s="9"/>
-      <c r="AG58" s="5"/>
+      <c r="AG58" s="5">
+        <v>-101.3</v>
+      </c>
       <c r="AH58" s="10">
         <v>2</v>
       </c>
@@ -15457,7 +15491,7 @@
         <v>0</v>
       </c>
       <c r="AH111" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI111" s="11"/>
       <c r="AJ111" s="13">
@@ -15810,7 +15844,7 @@
         <v>-245.80000000000001</v>
       </c>
       <c r="AH114" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI114" s="11"/>
       <c r="AJ114" s="13">
@@ -16983,7 +17017,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17376,7 +17410,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18553,7 +18587,7 @@
         <v>0</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -20857,7 +20891,7 @@
         <v>-3191.3499999999999</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -22141,7 +22175,7 @@
         <v>-66.900000000000006</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -24219,7 +24253,9 @@
       <c r="AB179" s="8">
         <v>0.88070000000000004</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>3.8850859999999998</v>
+      </c>
       <c r="AD179" s="8">
         <v>10.852631578947367</v>
       </c>
@@ -28304,7 +28340,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-03).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-03).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-182</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>R$ 874.451,26</t>
-  </si>
-  <si>
-    <t>R$ 4.554,43
-R$ 4.642,36</t>
-  </si>
-  <si>
-    <t>(3.9%)
-(2.0%)</t>
-  </si>
-  <si>
-    <t>50.0</t>
+186</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>R$ 887.720,87</t>
+  </si>
+  <si>
+    <t>R$ 4.529,19
+R$ 4.613,87</t>
+  </si>
+  <si>
+    <t>(4.0%)
+(2.2%)</t>
+  </si>
+  <si>
+    <t>49.7</t>
   </si>
   <si>
     <t>(9.6%)</t>
   </si>
   <si>
-    <t>(14.2%)</t>
-  </si>
-  <si>
-    <t>(54.7%)</t>
+    <t>(15.8%)</t>
+  </si>
+  <si>
+    <t>(56.2%)</t>
   </si>
   <si>
     <t>3.9%</t>
@@ -947,19 +947,19 @@
     <t>0.5%</t>
   </si>
   <si>
-    <t>26.8</t>
+    <t>26.9</t>
   </si>
   <si>
     <t>74.0%</t>
   </si>
   <si>
-    <t>9.9%</t>
+    <t>10.1%</t>
   </si>
   <si>
     <t>5.2</t>
   </si>
   <si>
-    <t>6.8</t>
+    <t>6.9</t>
   </si>
   <si>
     <t>12.3</t>
@@ -968,13 +968,13 @@
     <t>18.8</t>
   </si>
   <si>
-    <t>72.9%</t>
+    <t>72.6%</t>
   </si>
   <si>
     <t>-R$ 28.390,15</t>
   </si>
   <si>
-    <t>2.95</t>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -4424,7 +4424,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4460,25 +4460,59 @@
       <c t="s" r="N24" s="4">
         <v>52</v>
       </c>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
+      <c r="O24" s="5">
+        <v>3958.27</v>
+      </c>
+      <c r="P24" s="5">
+        <v>3958.27</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>0.1352547408996525</v>
+      </c>
+      <c r="R24" s="7">
+        <v>43</v>
+      </c>
+      <c r="S24" s="6">
+        <v>-0.085106382978723416</v>
+      </c>
+      <c r="T24" s="6">
+        <v>-5.6459726597730819</v>
+      </c>
+      <c r="U24" s="6">
+        <v>-5.976859638175263</v>
+      </c>
+      <c r="V24" s="6">
+        <v>0.028655574278662145</v>
+      </c>
+      <c r="W24" s="6">
+        <v>-0.0056447640004345326</v>
+      </c>
+      <c r="X24" s="8">
+        <v>37.763513513513516</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>0.51351351351351349</v>
+      </c>
+      <c r="Z24" s="6">
+        <v>0.40540540540540543</v>
+      </c>
+      <c r="AA24" s="8">
+        <v>4.7515880952380956</v>
+      </c>
+      <c r="AB24" s="8">
+        <v>16.653602702702702</v>
+      </c>
       <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="6"/>
+      <c r="AD24" s="8">
+        <v>28.358559459459457</v>
+      </c>
+      <c r="AE24" s="6">
+        <v>0.29729729729729731</v>
+      </c>
       <c r="AF24" s="9"/>
-      <c r="AG24" s="5"/>
+      <c r="AG24" s="5">
+        <v>0</v>
+      </c>
       <c r="AH24" s="10">
         <v>2</v>
       </c>
@@ -5960,7 +5994,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5996,25 +6030,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>4297.6999999999998</v>
+      </c>
+      <c r="P36" s="5">
+        <v>4297.6999999999998</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.017496093565036119</v>
+      </c>
+      <c r="R36" s="7">
+        <v>60</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.39534883720930236</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.40350759708681389</v>
+      </c>
+      <c r="U36" s="6">
+        <v>0.069289294273681273</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.10194732065988785</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.053521418433115392</v>
+      </c>
+      <c r="X36" s="8">
+        <v>26.022727272727273</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.11363636363636363</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>5.4755741379310345</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>5.6139534883720934</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>10.865468</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>17.626515909090909</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.81818181818181823</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -7881,7 +7951,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7917,25 +7987,61 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="O51" s="5">
+        <v>425.19999999999999</v>
+      </c>
+      <c r="P51" s="5">
+        <v>425.19999999999999</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.03121439963545225</v>
+      </c>
+      <c r="R51" s="7">
+        <v>4</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.33333333333333337</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.33864063969896524</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.074693085606773277</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.22636523988711196</v>
+      </c>
+      <c r="X51" s="8">
+        <v>22.133299999999998</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>2.9375</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>6.0833000000000004</v>
+      </c>
+      <c r="AC51" s="8">
+        <v>11.183332999999999</v>
+      </c>
+      <c r="AD51" s="8">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>1</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -12640,7 +12746,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12679,7 +12785,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12713,25 +12819,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>4588.4399999999996</v>
+      </c>
+      <c r="P89" s="5">
+        <v>4588.4399999999996</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.34079536589675852</v>
+      </c>
+      <c r="R89" s="7">
+        <v>44</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.3623188405797102</v>
+      </c>
+      <c r="T89" s="6">
+        <v>1.0075182850816402</v>
+      </c>
+      <c r="U89" s="6">
+        <v>0.69102945663449888</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.0181097497188587</v>
+      </c>
+      <c r="W89" s="6">
+        <v>-0.0056630358030180196</v>
+      </c>
+      <c r="X89" s="8">
+        <v>29.535803703703703</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.70370370370370372</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>4.6311586956521742</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>6.8025653846153853</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>19.995677777777775</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.48148148148148145</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -16755,7 +16895,7 @@
         <v>0</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -18718,7 +18858,7 @@
         <v>-565.79999999999995</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -21018,7 +21158,7 @@
         <v>0</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
